--- a/Luca/luca_bert_rag_results.xlsx
+++ b/Luca/luca_bert_rag_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,68 +1503,268 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.354838709677419</v>
       </c>
       <c r="K11" t="n">
         <v>15.1182815336412</v>
       </c>
       <c r="L11" t="n">
-        <v>15.11281535702367</v>
+        <v>15.1128153570237</v>
       </c>
       <c r="M11" t="n">
-        <v>0.005369732456822549</v>
+        <v>0.00536973245682255</v>
       </c>
       <c r="N11" t="n">
-        <v>13.03280175815929</v>
+        <v>13.0328017581593</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.545454545454545</v>
       </c>
       <c r="P11" t="n">
-        <v>13.02742873538624</v>
+        <v>13.0274287353862</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.005271608179265802</v>
+        <v>0.0052716081792658</v>
       </c>
       <c r="R11" t="n">
-        <v>17.44106928507487</v>
+        <v>17.4410692850749</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="T11" t="n">
-        <v>17.43529367446899</v>
+        <v>17.435293674469</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005671779314676921</v>
+        <v>0.00567177931467692</v>
       </c>
       <c r="V11" t="n">
-        <v>17.58758762904576</v>
+        <v>17.5875876290458</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="X11" t="n">
-        <v>17.58229463441031</v>
+        <v>17.5822946344103</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.005204405103410993</v>
+        <v>0.00520440510341099</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.93519701276507</v>
+        <v>13.9351970127651</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.92967649868556</v>
+        <v>13.9296764986856</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.005430357796805245</v>
+        <v>0.00543035779680525</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>2026-05-14 14:35:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>89adeff3dab244b5897f698e774924c2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BERT + RAG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>rag</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BAAI/bge-small-en-v1.5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18.2682171861331</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18.2626298964024</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.00541234016418457</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17.121810823679</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="P12" t="n">
+        <v>17.116189956665</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0054926872253418</v>
+      </c>
+      <c r="R12" t="n">
+        <v>19.6816903750102</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>19.675488114357</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.00605714321136475</v>
+      </c>
+      <c r="V12" t="n">
+        <v>18.6171196937561</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>18.6118224143982</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.00494551658630371</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>18.0573970317841</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>18.0523114204407</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.00497684478759766</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2c840d874e6f49d9ac9b408eb4843ad5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Luca</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BERT + RAG</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>rag</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nomic-ai/nomic-embed-text-v1.5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>30.79813647270203</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.79298985004425</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.005051159858703613</v>
+      </c>
+      <c r="N13" t="n">
+        <v>28.72123730182648</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>28.71610713005066</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.005020856857299805</v>
+      </c>
+      <c r="R13" t="n">
+        <v>21.82971274852753</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>21.82440745830536</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.005232930183410645</v>
+      </c>
+      <c r="V13" t="n">
+        <v>39.60978182156881</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>39.60451094309489</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.005180517832438151</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>29.35003972053528</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>29.34511216481527</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.004820823669433594</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-05-14 16:19:52</t>
         </is>
       </c>
     </row>
